--- a/backend/stored_queries/files/inventory_data.xlsx
+++ b/backend/stored_queries/files/inventory_data.xlsx
@@ -138,4 +138,918 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="1F497D"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="EEECE1"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4F81BD"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="C0504D"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="9BBB59"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8064A2"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4BACC6"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="F79646"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000FF"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="800080"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+</a:theme>
+</file>
+
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Product ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Product Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Stock Quantity</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Unit Cost</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Supplier</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Last Updated</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Product 1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>217</v>
+      </c>
+      <c r="E2" t="n">
+        <v>33.04</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Supplier A</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>45292</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Product 2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>424</v>
+      </c>
+      <c r="E3" t="n">
+        <v>172.77</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Supplier B</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>45293</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Product 3</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>945</v>
+      </c>
+      <c r="E4" t="n">
+        <v>112.24</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Supplier A</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>45294</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Product 4</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>408</v>
+      </c>
+      <c r="E5" t="n">
+        <v>7.05</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Supplier B</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>45295</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Product 5</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Electronics</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>339</v>
+      </c>
+      <c r="E6" t="n">
+        <v>68.47</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Supplier C</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>45296</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Product 6</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>718</v>
+      </c>
+      <c r="E7" t="n">
+        <v>159.31</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Supplier A</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>45297</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Product 7</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Clothing</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>919</v>
+      </c>
+      <c r="E8" t="n">
+        <v>187.95</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Supplier A</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>45298</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Product 8</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Electronics</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>478</v>
+      </c>
+      <c r="E9" t="n">
+        <v>164.07</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Supplier A</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>45299</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Product 9</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>265</v>
+      </c>
+      <c r="E10" t="n">
+        <v>43.36</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Supplier C</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>45300</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Product 10</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>643</v>
+      </c>
+      <c r="E11" t="n">
+        <v>169.55</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Supplier B</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>45301</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Product 11</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Clothing</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>96</v>
+      </c>
+      <c r="E12" t="n">
+        <v>148</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Supplier B</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>45302</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Product 12</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Clothing</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>994</v>
+      </c>
+      <c r="E13" t="n">
+        <v>140.76</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Supplier B</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>45303</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Product 13</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Clothing</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>339</v>
+      </c>
+      <c r="E14" t="n">
+        <v>29.34</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Supplier B</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>45304</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Product 14</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>758</v>
+      </c>
+      <c r="E15" t="n">
+        <v>121.84</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Supplier B</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>45305</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Product 15</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Electronics</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>600</v>
+      </c>
+      <c r="E16" t="n">
+        <v>78.36</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Supplier C</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>45306</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Product 16</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>732</v>
+      </c>
+      <c r="E17" t="n">
+        <v>129.37</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Supplier B</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>45307</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Product 17</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Clothing</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>754</v>
+      </c>
+      <c r="E18" t="n">
+        <v>142.13</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Supplier A</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>45308</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Product 18</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Electronics</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>691</v>
+      </c>
+      <c r="E19" t="n">
+        <v>137.87</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Supplier C</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>45309</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Product 19</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Electronics</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>770</v>
+      </c>
+      <c r="E20" t="n">
+        <v>36.31</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Supplier C</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>45310</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Product 20</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Electronics</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>727</v>
+      </c>
+      <c r="E21" t="n">
+        <v>87.81999999999999</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Supplier A</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>45311</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>